--- a/docs/generated/Контакты.xlsx
+++ b/docs/generated/Контакты.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>

--- a/docs/generated/Контакты.xlsx
+++ b/docs/generated/Контакты.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>125000</v>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>64000</v>

--- a/docs/generated/Контакты.xlsx
+++ b/docs/generated/Контакты.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>125000</v>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>64000</v>

--- a/docs/generated/Контакты.xlsx
+++ b/docs/generated/Контакты.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>125000</v>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>64000</v>
